--- a/eml_XSLT/mappingtable_EML.xlsx
+++ b/eml_XSLT/mappingtable_EML.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/congjulia/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/congjulia/Discipline-DataCite/eml_XSLT/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB7D488A-D090-0141-BE13-B4A12F17BD02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2407B4C-6D46-4048-BE63-2ED7EC8C2647}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9160" yWindow="860" windowWidth="19680" windowHeight="17360" xr2:uid="{B56C2A0C-4212-1F44-ACF1-ACB76C2E05C5}"/>
+    <workbookView xWindow="140" yWindow="820" windowWidth="19680" windowHeight="17360" xr2:uid="{B56C2A0C-4212-1F44-ACF1-ACB76C2E05C5}"/>
   </bookViews>
   <sheets>
     <sheet name="EML→DataCite" sheetId="1" r:id="rId1"/>
@@ -754,24 +754,27 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>eml&gt;dataset&gt;creator</t>
-  </si>
-  <si>
     <t>eml&gt;dataset&gt;title</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>eml&gt;dataset&gt;publisher&gt; organizationName&gt;value</t>
-  </si>
-  <si>
-    <t>eml&gt;dataset&gt;PubDate</t>
-  </si>
-  <si>
     <t>"Dataset"に相当する、と想定</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>｛IDはDOI形式に限定されない｝</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>eml&gt;dataset&gt;creator</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>eml&gt;dataset&gt;publisher&gt; organizationName&gt;value</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>eml&gt;dataset&gt;PubDate</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1626,7 +1629,7 @@
         <v>1</v>
       </c>
       <c r="I2" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -1663,7 +1666,7 @@
         <v>13</v>
       </c>
       <c r="I4" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -1860,7 +1863,7 @@
         <v>13</v>
       </c>
       <c r="I16" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -1897,7 +1900,7 @@
         <v>1</v>
       </c>
       <c r="I18" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -1966,7 +1969,7 @@
         <v>1</v>
       </c>
       <c r="I22" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -2347,7 +2350,7 @@
         <v>1</v>
       </c>
       <c r="I45" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
     </row>
     <row r="46" spans="1:9">
